--- a/tools/example_framework.xlsx
+++ b/tools/example_framework.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0802E0-1F60-44ED-B43C-F0E92A8F8725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FC5D82-7489-4EE8-8B11-F9DBFD503FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="946" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="6" r:id="rId1"/>
@@ -772,7 +772,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="564">
   <si>
     <t>type</t>
   </si>
@@ -842,12 +842,6 @@
     <t>Il s'agit d'un framework de démonstration.
 Il présente des exemples de règles, de contrôles et d'exigences.
 Il est conçu pour illustrer.</t>
-  </si>
-  <si>
-    <t>copyright[fr]</t>
-  </si>
-  <si>
-    <t>© 2025 Entreprise d'Exemple</t>
   </si>
   <si>
     <t>framework</t>
@@ -2740,6 +2734,33 @@
     </r>
   </si>
   <si>
+    <t>scr_binary</t>
+  </si>
+  <si>
+    <t>Not achieved</t>
+  </si>
+  <si>
+    <t>The requirement is not achieved.</t>
+  </si>
+  <si>
+    <t>Non atteint</t>
+  </si>
+  <si>
+    <t>L'exigence n'est pas atteinte.</t>
+  </si>
+  <si>
+    <t>Achieved</t>
+  </si>
+  <si>
+    <t>The requirement is achieved.</t>
+  </si>
+  <si>
+    <t>Atteint</t>
+  </si>
+  <si>
+    <t>L'exigence est atteinte.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">When creating a library, keep only the tabs that are necessary. For example, if no implementation groups are used, remove the corresponding tabs. The text preceding </t>
     </r>
@@ -2789,7 +2810,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> can be replaced with the text of your choice (e.g. you can write </t>
+      <t xml:space="preserve"> can be replaced with the text of your choice (e.g., you can write </t>
     </r>
     <r>
       <rPr>
@@ -2839,33 +2860,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>scr_binary</t>
-  </si>
-  <si>
-    <t>Not achieved</t>
-  </si>
-  <si>
-    <t>The requirement is not achieved.</t>
-  </si>
-  <si>
-    <t>Non atteint</t>
-  </si>
-  <si>
-    <t>L'exigence n'est pas atteinte.</t>
-  </si>
-  <si>
-    <t>Achieved</t>
-  </si>
-  <si>
-    <t>The requirement is achieved.</t>
-  </si>
-  <si>
-    <t>Atteint</t>
-  </si>
-  <si>
-    <t>L'exigence est atteinte.</t>
   </si>
 </sst>
 </file>
@@ -3578,6 +3572,87 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3596,24 +3671,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3623,15 +3680,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3649,175 +3697,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="73">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -4307,14 +4192,14 @@
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -4354,6 +4239,55 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
@@ -4643,6 +4577,66 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4911,39 +4905,39 @@
     <tableColumn id="7" xr3:uid="{E61773D4-D778-4312-A49F-8A5758A995E8}" name="typical_evidence" dataDxfId="61"/>
     <tableColumn id="18" xr3:uid="{B81C882B-0E05-4883-AAC0-A9708505EABA}" name="importance" dataDxfId="60"/>
     <tableColumn id="17" xr3:uid="{87B98E78-198B-4AAF-BD74-A0DD4AE4E732}" name="weight" dataDxfId="59"/>
-    <tableColumn id="22" xr3:uid="{C5CECF0A-2791-4172-BCD1-16A78E34ED94}" name="min_score" dataDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{97B7A8A1-8AB0-4C26-A50A-B063EE3BEADA}" name="max_score" dataDxfId="0"/>
-    <tableColumn id="24" xr3:uid="{D0C80AC0-733E-4515-824A-A8639FDEBD4C}" name="scores_definition" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{41549C1C-81F1-4DC9-AF3E-D66557AB55EA}" name="implementation_groups" dataDxfId="58"/>
-    <tableColumn id="14" xr3:uid="{AFF985E6-291A-441C-8DEF-8F4448E20722}" name="questions" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{22C6C123-59A8-4006-974A-AEC9BDF7B9C5}" name="answer" dataDxfId="56"/>
-    <tableColumn id="15" xr3:uid="{98B369E5-A92E-4F40-ABC5-965BF81E342E}" name="threats" dataDxfId="55"/>
-    <tableColumn id="16" xr3:uid="{12E0FCEA-DE2D-4475-972C-17BB204562B1}" name="reference_controls" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{D92464D6-5A4E-46A6-B30C-5054FBC689EF}" name="name[fr]" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{582EF74A-B398-41A0-ACCF-D0452C1A56EF}" name="description[fr]" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{EA0E2718-3825-4A77-B686-8C594E64AC01}" name="annotation[fr]" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{CB66FA06-DCF3-44C6-A079-7B12A457972F}" name="typical_evidence[fr]" dataDxfId="50"/>
+    <tableColumn id="22" xr3:uid="{C5CECF0A-2791-4172-BCD1-16A78E34ED94}" name="min_score" dataDxfId="58"/>
+    <tableColumn id="25" xr3:uid="{97B7A8A1-8AB0-4C26-A50A-B063EE3BEADA}" name="max_score" dataDxfId="57"/>
+    <tableColumn id="24" xr3:uid="{D0C80AC0-733E-4515-824A-A8639FDEBD4C}" name="scores_definition" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{41549C1C-81F1-4DC9-AF3E-D66557AB55EA}" name="implementation_groups" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{AFF985E6-291A-441C-8DEF-8F4448E20722}" name="questions" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{22C6C123-59A8-4006-974A-AEC9BDF7B9C5}" name="answer" dataDxfId="53"/>
+    <tableColumn id="15" xr3:uid="{98B369E5-A92E-4F40-ABC5-965BF81E342E}" name="threats" dataDxfId="52"/>
+    <tableColumn id="16" xr3:uid="{12E0FCEA-DE2D-4475-972C-17BB204562B1}" name="reference_controls" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{D92464D6-5A4E-46A6-B30C-5054FBC689EF}" name="name[fr]" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{582EF74A-B398-41A0-ACCF-D0452C1A56EF}" name="description[fr]" dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{EA0E2718-3825-4A77-B686-8C594E64AC01}" name="annotation[fr]" dataDxfId="48"/>
+    <tableColumn id="12" xr3:uid="{CB66FA06-DCF3-44C6-A079-7B12A457972F}" name="typical_evidence[fr]" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{095154CE-6DE0-439C-B5AB-1118C37DCAF4}" name="Tableau2" displayName="Tableau2" ref="A1:E5" totalsRowShown="0" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{095154CE-6DE0-439C-B5AB-1118C37DCAF4}" name="Tableau2" displayName="Tableau2" ref="A1:E5" totalsRowShown="0" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="A1:E5" xr:uid="{095154CE-6DE0-439C-B5AB-1118C37DCAF4}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BB7E1ECB-4B2B-4222-B69C-FDF7FCF7F451}" name="ref_id" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{AA129DE3-6969-4BE8-8FD1-B74529AF31A8}" name="name" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{7980BF69-F795-4B15-9518-5B07FE2675D7}" name="description" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{245E3F68-8E07-4115-ADB2-6D2D1DB60F36}" name="name[fr]" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{7C50CF1F-76A2-4CDB-B985-67AE9549E305}" name="description[fr]" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{BB7E1ECB-4B2B-4222-B69C-FDF7FCF7F451}" name="ref_id" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{AA129DE3-6969-4BE8-8FD1-B74529AF31A8}" name="name" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{7980BF69-F795-4B15-9518-5B07FE2675D7}" name="description" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{245E3F68-8E07-4115-ADB2-6D2D1DB60F36}" name="name[fr]" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{7C50CF1F-76A2-4CDB-B985-67AE9549E305}" name="description[fr]" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="Style de tableau 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C7B78881-4183-44AE-BDF4-F6BDECF9D936}" name="Tableau4" displayName="Tableau4" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C7B78881-4183-44AE-BDF4-F6BDECF9D936}" name="Tableau4" displayName="Tableau4" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="37">
   <autoFilter ref="A1:C1048576" xr:uid="{C7B78881-4183-44AE-BDF4-F6BDECF9D936}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F801AE0F-E094-475A-BBD2-F4BED2F83A76}" name="id"/>
@@ -4955,7 +4949,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8AB0205B-E51F-4004-809C-4673837E5B05}" name="Tableau5" displayName="Tableau5" ref="A1:E1048576" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8AB0205B-E51F-4004-809C-4673837E5B05}" name="Tableau5" displayName="Tableau5" ref="A1:E1048576" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34">
   <autoFilter ref="A1:E1048576" xr:uid="{8AB0205B-E51F-4004-809C-4673837E5B05}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{881914C9-040C-42B4-91FE-05BC90988F70}" name="score"/>
@@ -4969,7 +4963,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D0D135C9-AB17-4523-8979-B32021DF2E8F}" name="Tableau57" displayName="Tableau57" ref="A1:E1048572" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D0D135C9-AB17-4523-8979-B32021DF2E8F}" name="Tableau57" displayName="Tableau57" ref="A1:E1048572" totalsRowShown="0" headerRowDxfId="33" headerRowBorderDxfId="32" tableBorderDxfId="31">
   <autoFilter ref="A1:E1048572" xr:uid="{8AB0205B-E51F-4004-809C-4673837E5B05}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3C97C9BD-CC3B-4BD6-92B0-0FCE548DC4F4}" name="score"/>
@@ -4983,45 +4977,45 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21DED0C8-7237-47BF-8873-738C4400D3DB}" name="Tableau14" displayName="Tableau14" ref="A1:G26" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21DED0C8-7237-47BF-8873-738C4400D3DB}" name="Tableau14" displayName="Tableau14" ref="A1:G26" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="A1:G26" xr:uid="{32B00483-E3F9-4C14-B125-41886D9D0F23}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2F9E1637-D442-4022-8B78-23492F1B2FD4}" name="ref_id" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{1990900A-E9A9-4853-8F63-DC439067075E}" name="name" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{E03E16C2-E13E-458D-A24A-3C34A91E3DF2}" name="description" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{5ECFEFFA-B045-45BD-A6D7-4E11C3283380}" name="annotation" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{4F645D7B-245A-416B-9E6F-06323318E6E2}" name="name[fr]" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{E7094BA8-F77D-4F12-A3F8-7928936A0D2E}" name="description[fr]" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{B9C14FC4-B603-427E-A7F4-CACF10F7A085}" name="annotation[fr]" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{2F9E1637-D442-4022-8B78-23492F1B2FD4}" name="ref_id" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{1990900A-E9A9-4853-8F63-DC439067075E}" name="name" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{E03E16C2-E13E-458D-A24A-3C34A91E3DF2}" name="description" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{5ECFEFFA-B045-45BD-A6D7-4E11C3283380}" name="annotation" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{4F645D7B-245A-416B-9E6F-06323318E6E2}" name="name[fr]" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{E7094BA8-F77D-4F12-A3F8-7928936A0D2E}" name="description[fr]" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{B9C14FC4-B603-427E-A7F4-CACF10F7A085}" name="annotation[fr]" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="Style de tableau 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6DCAA1FD-DB86-4E15-8E31-AC99AB9F45D4}" name="Tableau3" displayName="Tableau3" ref="A1:I27" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6DCAA1FD-DB86-4E15-8E31-AC99AB9F45D4}" name="Tableau3" displayName="Tableau3" ref="A1:I27" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:I27" xr:uid="{4748F8BA-F2F9-4976-90F0-1D6F9F26191B}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{15A5B4EF-24CA-4813-9A39-8D55A540B838}" name="ref_id" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{541E38F3-C3CB-49DA-B177-2A1749008A5B}" name="name" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{F2BC8545-6F89-4E86-8E77-5E4AA7C0033E}" name="category" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{2D6C7622-7C26-46E8-BA06-DC874E602ECA}" name="csf_function" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{8B114798-8119-45A5-AC98-80691A7F5743}" name="description" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{3B24CD29-2024-4E6C-8EA8-A2A27F71DB45}" name="annotation" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{6D87C08C-7195-4695-A258-EC8C5FBA7769}" name="name[fr]" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{05DA7DF2-5885-4810-9061-18E2243F317E}" name="description[fr]" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{4E63784C-6489-4DCD-AFDF-2126BE436F13}" name="annotation[fr]" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{15A5B4EF-24CA-4813-9A39-8D55A540B838}" name="ref_id" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{541E38F3-C3CB-49DA-B177-2A1749008A5B}" name="name" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{F2BC8545-6F89-4E86-8E77-5E4AA7C0033E}" name="category" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{2D6C7622-7C26-46E8-BA06-DC874E602ECA}" name="csf_function" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{8B114798-8119-45A5-AC98-80691A7F5743}" name="description" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{3B24CD29-2024-4E6C-8EA8-A2A27F71DB45}" name="annotation" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{6D87C08C-7195-4695-A258-EC8C5FBA7769}" name="name[fr]" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{05DA7DF2-5885-4810-9061-18E2243F317E}" name="description[fr]" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{4E63784C-6489-4DCD-AFDF-2126BE436F13}" name="annotation[fr]" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Style de tableau 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D16BDFCB-B8D2-4F9D-906C-2230193C4279}" name="Tableau7" displayName="Tableau7" ref="A1:B4" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D16BDFCB-B8D2-4F9D-906C-2230193C4279}" name="Tableau7" displayName="Tableau7" ref="A1:B4" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:B4" xr:uid="{D16BDFCB-B8D2-4F9D-906C-2230193C4279}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{438C028E-BBB1-42A6-99B2-250AC16AFAC2}" name="prefix_id" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{A29B1659-A5F7-4CB7-96A6-4F3536BCB6B5}" name="prefix_value" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{438C028E-BBB1-42A6-99B2-250AC16AFAC2}" name="prefix_id" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{A29B1659-A5F7-4CB7-96A6-4F3536BCB6B5}" name="prefix_value" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Style de tableau 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5323,399 +5317,421 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="62.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="105"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="99"/>
     </row>
     <row r="2" spans="1:13" ht="42.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="106" t="s">
-        <v>543</v>
-      </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="108"/>
+      <c r="A2" s="100" t="s">
+        <v>541</v>
+      </c>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="102"/>
     </row>
     <row r="3" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="105"/>
+    </row>
+    <row r="4" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="82"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="93" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="80" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="82"/>
+    </row>
+    <row r="6" spans="1:13" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="96" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="82"/>
+    </row>
+    <row r="7" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="92" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="82"/>
+    </row>
+    <row r="8" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="91" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="80" t="s">
+        <v>264</v>
+      </c>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="82"/>
+    </row>
+    <row r="9" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="79" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="80" t="s">
+        <v>266</v>
+      </c>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="82"/>
+    </row>
+    <row r="10" spans="1:13" ht="33.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="79" t="s">
+        <v>552</v>
+      </c>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="85"/>
+    </row>
+    <row r="11" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="86" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="80" t="s">
+        <v>265</v>
+      </c>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="82"/>
+    </row>
+    <row r="12" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="87" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="80" t="s">
+        <v>275</v>
+      </c>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="82"/>
+    </row>
+    <row r="13" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="88" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="80" t="s">
+        <v>276</v>
+      </c>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="82"/>
+    </row>
+    <row r="14" spans="1:13" ht="34.799999999999997" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="106"/>
+      <c r="C14" s="107" t="s">
+        <v>563</v>
+      </c>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+    </row>
+    <row r="15" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
-    </row>
-    <row r="4" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="112" t="s">
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="105"/>
+    </row>
+    <row r="16" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="118" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="87"/>
-    </row>
-    <row r="5" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="94" t="s">
+      <c r="B16" s="119"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="82"/>
+    </row>
+    <row r="17" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="80" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="85" t="s">
-        <v>264</v>
-      </c>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="87"/>
-    </row>
-    <row r="6" spans="1:13" ht="19.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="117" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="85" t="s">
-        <v>265</v>
-      </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="87"/>
-    </row>
-    <row r="7" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="116" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="85" t="s">
-        <v>274</v>
-      </c>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="87"/>
-    </row>
-    <row r="8" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="115" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" s="115"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="85" t="s">
-        <v>266</v>
-      </c>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="87"/>
-    </row>
-    <row r="9" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="114" t="s">
-        <v>255</v>
-      </c>
-      <c r="B9" s="114"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="85" t="s">
-        <v>268</v>
-      </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="87"/>
-    </row>
-    <row r="10" spans="1:13" ht="33.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="114" t="s">
-        <v>554</v>
-      </c>
-      <c r="B10" s="114"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="118" t="s">
-        <v>555</v>
-      </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="120"/>
-    </row>
-    <row r="11" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="109" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="109"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="85" t="s">
-        <v>267</v>
-      </c>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="87"/>
-    </row>
-    <row r="12" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="110" t="s">
-        <v>272</v>
-      </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="85" t="s">
-        <v>277</v>
-      </c>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="87"/>
-    </row>
-    <row r="13" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="111" t="s">
-        <v>273</v>
-      </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="85" t="s">
-        <v>278</v>
-      </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="87"/>
-    </row>
-    <row r="14" spans="1:13" ht="34.799999999999997" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79" t="s">
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="82"/>
+    </row>
+    <row r="18" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="115" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="80" t="s">
+        <v>258</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="82"/>
+    </row>
+    <row r="19" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="80" t="s">
-        <v>556</v>
-      </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-    </row>
-    <row r="15" spans="1:13" ht="34.799999999999997" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="88" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="90"/>
-    </row>
-    <row r="16" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100" t="s">
-        <v>258</v>
-      </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="85" t="s">
-        <v>263</v>
-      </c>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="87"/>
-    </row>
-    <row r="17" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="94" t="s">
+      <c r="B19" s="113"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="80" t="s">
+        <v>259</v>
+      </c>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="82"/>
+    </row>
+    <row r="20" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="109" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="110"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="85" t="s">
-        <v>259</v>
-      </c>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="87"/>
-    </row>
-    <row r="18" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="97" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="85" t="s">
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="82"/>
+    </row>
+    <row r="21" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="106" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="106"/>
+      <c r="C21" s="107" t="s">
         <v>260</v>
       </c>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="87"/>
-    </row>
-    <row r="19" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="91" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="85" t="s">
-        <v>261</v>
-      </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="87"/>
-    </row>
-    <row r="20" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="82" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="85" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="87"/>
-    </row>
-    <row r="21" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="79" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80" t="s">
-        <v>262</v>
-      </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
     </row>
     <row r="22" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:M21"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="G20:M20"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="G19:M19"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="G17:M17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G18:M18"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="G16:M16"/>
+    <mergeCell ref="G5:M5"/>
+    <mergeCell ref="G6:M6"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="G8:M8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="G9:M9"/>
     <mergeCell ref="G10:M10"/>
@@ -5732,28 +5748,6 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G5:M5"/>
-    <mergeCell ref="G6:M6"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="G8:M8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:M21"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="G20:M20"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:M14"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G19:M19"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="G17:M17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G18:M18"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="G16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5777,7 +5771,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>10</v>
@@ -5798,16 +5792,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F2" s="47"/>
       <c r="G2" s="48"/>
@@ -5817,16 +5811,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="48"/>
@@ -5836,16 +5830,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="48"/>
@@ -5855,16 +5849,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F5" s="47"/>
       <c r="G5" s="48"/>
@@ -5874,16 +5868,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
@@ -5893,16 +5887,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
@@ -5934,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -5942,7 +5936,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -5968,7 +5962,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>10</v>
@@ -5989,16 +5983,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>557</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>558</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>559</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>560</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>561</v>
       </c>
       <c r="F2" s="47"/>
       <c r="G2" s="48"/>
@@ -6008,16 +6002,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>560</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>561</v>
+      </c>
+      <c r="E3" s="51" t="s">
         <v>562</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>563</v>
-      </c>
-      <c r="D3" s="50" t="s">
-        <v>564</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>565</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="48"/>
@@ -6050,15 +6044,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -6096,7 +6090,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E1" s="65" t="s">
         <v>18</v>
@@ -6105,564 +6099,564 @@
         <v>20</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D3" s="31"/>
       <c r="E3" s="60" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>340</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="G4" s="31" t="s">
         <v>443</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>445</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="63" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="60" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="63" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="E6" s="60" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="63" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="E7" s="60" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="63" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="E8" s="60" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="E9" s="60" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="63" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="63" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="63" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="63" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="31" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="63" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D15" s="31"/>
       <c r="E15" s="31" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="63" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="31" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="63" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="63" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="63" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="63" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B20" s="60" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C20" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="D20" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>336</v>
-      </c>
       <c r="E20" s="60" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="63" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B21" s="60" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="60" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="63" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B22" s="60" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C22" s="66"/>
       <c r="D22" s="31" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E22" s="60" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F22" s="66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G22" s="66" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="63" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C23" s="66"/>
       <c r="D23" s="66"/>
       <c r="E23" s="60" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G23" s="66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="63" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C24" s="66"/>
       <c r="D24" s="66"/>
       <c r="E24" s="60" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="63" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B25" s="60" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="60" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="63" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B26" s="60" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="60" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -6694,15 +6688,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -6737,16 +6731,16 @@
         <v>10</v>
       </c>
       <c r="C1" s="64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E1" s="62" t="s">
         <v>12</v>
       </c>
       <c r="F1" s="74" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1" s="65" t="s">
         <v>18</v>
@@ -6755,617 +6749,617 @@
         <v>20</v>
       </c>
       <c r="I1" s="65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
       <c r="E2" s="31" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H2" s="31" t="s">
+        <v>494</v>
+      </c>
+      <c r="I2" s="31" t="s">
         <v>496</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
       <c r="E3" s="31" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F3" s="31"/>
       <c r="G3" s="31" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
       <c r="F4" s="31" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D7" s="31"/>
       <c r="E7" s="31"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
       <c r="F9" s="66"/>
       <c r="G9" s="31" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="31"/>
       <c r="G10" s="31" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="31" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="31" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="31" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="31" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="31" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="31" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="31" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="31" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
       <c r="G20" s="31" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="31" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E21" s="31" t="s">
+        <v>509</v>
+      </c>
+      <c r="F21" s="31" t="s">
         <v>511</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>513</v>
-      </c>
       <c r="G21" s="31" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H21" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="I21" s="31" t="s">
         <v>472</v>
-      </c>
-      <c r="I21" s="31" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C22" s="31"/>
       <c r="D22" s="31"/>
       <c r="E22" s="31" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="31" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I22" s="31"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="31" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
       <c r="G24" s="31" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="31" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="31" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
       <c r="G27" s="31" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7394,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -7416,10 +7410,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -7427,15 +7421,15 @@
         <v>5</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -7443,7 +7437,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -7463,7 +7457,7 @@
   <sheetPr codeName="Feuil2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -7531,7 +7525,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -7552,18 +7546,18 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="78" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="78" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -7580,14 +7574,6 @@
       </c>
       <c r="B14" s="37" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -7613,15 +7599,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -7629,7 +7615,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -7658,42 +7644,42 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="52" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="52" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -7754,10 +7740,10 @@
   <sheetData>
     <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>8</v>
@@ -7769,40 +7755,40 @@
         <v>12</v>
       </c>
       <c r="F1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>546</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="M1" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="N1" s="38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O1" s="38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P1" s="69" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q1" s="75" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="R1" s="14" t="s">
         <v>18</v>
@@ -7811,10 +7797,10 @@
         <v>20</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
@@ -7823,11 +7809,11 @@
         <v>1</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D2" s="40"/>
       <c r="E2" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
@@ -7843,7 +7829,7 @@
       <c r="Q2" s="41"/>
       <c r="R2" s="40"/>
       <c r="S2" s="40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T2" s="40"/>
       <c r="U2" s="42"/>
@@ -7851,20 +7837,20 @@
     <row r="3" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39"/>
       <c r="B3" s="40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
@@ -7877,31 +7863,31 @@
       <c r="P3" s="41"/>
       <c r="Q3" s="41"/>
       <c r="R3" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S3" s="40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="T3" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="U3" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="39"/>
       <c r="B4" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>
@@ -7916,32 +7902,32 @@
       <c r="P4" s="41"/>
       <c r="Q4" s="41"/>
       <c r="R4" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="S4" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T4" s="40"/>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" s="40"/>
       <c r="D5" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
       <c r="H5" s="40" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I5" s="40"/>
       <c r="J5" s="40"/>
@@ -7949,84 +7935,84 @@
       <c r="L5" s="40"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="O5" s="36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P5" s="37"/>
       <c r="Q5" s="37"/>
       <c r="R5" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S5" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="T5" s="40"/>
       <c r="U5" s="42"/>
     </row>
     <row r="6" spans="1:21" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="40"/>
       <c r="D6" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J6" s="40"/>
       <c r="K6" s="40"/>
       <c r="L6" s="40"/>
       <c r="M6" s="40"/>
       <c r="N6" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="O6" s="36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P6" s="37"/>
       <c r="Q6" s="37"/>
       <c r="R6" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S6" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T6" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="U6" s="42"/>
     </row>
     <row r="7" spans="1:21" s="30" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" s="40"/>
       <c r="D7" s="40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F7" s="40"/>
       <c r="G7" s="40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
@@ -8035,43 +8021,43 @@
       <c r="L7" s="40"/>
       <c r="M7" s="40"/>
       <c r="N7" s="41" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O7" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P7" s="41"/>
       <c r="Q7" s="41"/>
       <c r="R7" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S7" s="40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="T7" s="40"/>
       <c r="U7" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" s="40"/>
       <c r="D8" s="40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
@@ -8082,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="40" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="M8" s="40"/>
       <c r="N8" s="40"/>
@@ -8090,34 +8076,34 @@
       <c r="P8" s="41"/>
       <c r="Q8" s="41"/>
       <c r="R8" s="40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="S8" s="40" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T8" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="U8" s="40" t="s">
         <v>165</v>
-      </c>
-      <c r="U8" s="40" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" s="40"/>
       <c r="D9" s="40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40"/>
       <c r="H9" s="40" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I9" s="40"/>
       <c r="J9" s="40"/>
@@ -8129,7 +8115,7 @@
       <c r="P9" s="41"/>
       <c r="Q9" s="41"/>
       <c r="R9" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S9" s="40"/>
       <c r="T9" s="40"/>
@@ -8137,14 +8123,14 @@
     </row>
     <row r="10" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" s="40"/>
       <c r="D10" s="40" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" s="40"/>
       <c r="F10" s="40"/>
@@ -8160,7 +8146,7 @@
       <c r="P10" s="41"/>
       <c r="Q10" s="41"/>
       <c r="R10" s="40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S10" s="40"/>
       <c r="T10" s="40"/>
@@ -8168,23 +8154,23 @@
     </row>
     <row r="11" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" s="40"/>
       <c r="D11" s="40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="40"/>
       <c r="H11" s="40"/>
       <c r="I11" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J11" s="40"/>
       <c r="K11" s="40"/>
@@ -8195,27 +8181,27 @@
       <c r="P11" s="41"/>
       <c r="Q11" s="41"/>
       <c r="R11" s="40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S11" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T11" s="40"/>
       <c r="U11" s="42"/>
     </row>
     <row r="12" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" s="40"/>
       <c r="D12" s="40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
@@ -8230,29 +8216,29 @@
       <c r="P12" s="41"/>
       <c r="Q12" s="41"/>
       <c r="R12" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S12" s="40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T12" s="40"/>
       <c r="U12" s="42"/>
     </row>
     <row r="13" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="40"/>
@@ -8267,10 +8253,10 @@
       <c r="P13" s="41"/>
       <c r="Q13" s="41"/>
       <c r="R13" s="40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S13" s="40" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T13" s="40"/>
       <c r="U13" s="42"/>
@@ -8278,11 +8264,11 @@
     <row r="14" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39"/>
       <c r="B14" s="40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="40"/>
       <c r="D14" s="40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E14" s="40"/>
       <c r="F14" s="40"/>
@@ -8297,10 +8283,10 @@
       <c r="O14" s="40"/>
       <c r="P14" s="41"/>
       <c r="Q14" s="41" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="R14" s="40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S14" s="40"/>
       <c r="T14" s="40"/>
@@ -8308,22 +8294,22 @@
     </row>
     <row r="15" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" s="40"/>
       <c r="D15" s="40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G15" s="40"/>
       <c r="H15" s="39" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I15" s="39">
         <v>5</v>
@@ -8332,85 +8318,85 @@
       <c r="K15" s="39"/>
       <c r="L15" s="39"/>
       <c r="M15" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="70"/>
       <c r="Q15" s="76" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R15" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S15" s="40"/>
       <c r="T15" s="40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="U15" s="42"/>
     </row>
     <row r="16" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
       <c r="G16" s="40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I16" s="39"/>
       <c r="J16" s="39"/>
       <c r="K16" s="39"/>
       <c r="L16" s="39"/>
       <c r="M16" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="70"/>
       <c r="Q16" s="70" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R16" s="40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="S16" s="40"/>
       <c r="T16" s="40"/>
       <c r="U16" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:21" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="40" t="s">
         <v>67</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="39"/>
@@ -8418,37 +8404,37 @@
       <c r="K17" s="39"/>
       <c r="L17" s="39"/>
       <c r="M17" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="70"/>
       <c r="Q17" s="70" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="R17" s="40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="S17" s="40"/>
       <c r="T17" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="U17" s="40" t="s">
         <v>169</v>
-      </c>
-      <c r="U17" s="40" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:21" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E18" s="40"/>
       <c r="F18" s="40"/>
@@ -8459,16 +8445,16 @@
       <c r="K18" s="40"/>
       <c r="L18" s="40"/>
       <c r="M18" s="40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N18" s="40"/>
       <c r="O18" s="40"/>
       <c r="P18" s="41"/>
       <c r="Q18" s="70" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="R18" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="S18" s="40"/>
       <c r="T18" s="40"/>
@@ -8476,16 +8462,16 @@
     </row>
     <row r="19" spans="1:21" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
@@ -8496,18 +8482,18 @@
       <c r="K19" s="39"/>
       <c r="L19" s="39"/>
       <c r="M19" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
       <c r="P19" s="45" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q19" s="70" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="R19" s="40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S19" s="40"/>
       <c r="T19" s="40"/>
@@ -8515,16 +8501,16 @@
     </row>
     <row r="20" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
@@ -8535,16 +8521,16 @@
       <c r="K20" s="39"/>
       <c r="L20" s="39"/>
       <c r="M20" s="17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="70"/>
       <c r="Q20" s="70" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="R20" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="S20" s="40"/>
       <c r="T20" s="40"/>
@@ -8552,14 +8538,14 @@
     </row>
     <row r="21" spans="1:21" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" s="40"/>
       <c r="D21" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E21" s="40"/>
       <c r="F21" s="40"/>
@@ -8574,10 +8560,10 @@
       <c r="O21" s="40"/>
       <c r="P21" s="41"/>
       <c r="Q21" s="41" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R21" s="40" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S21" s="40"/>
       <c r="T21" s="40"/>
@@ -8586,14 +8572,14 @@
     <row r="22" spans="1:21" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39"/>
       <c r="B22" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22" s="40"/>
       <c r="D22" s="40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="40"/>
@@ -8603,33 +8589,33 @@
       <c r="K22" s="40"/>
       <c r="L22" s="40"/>
       <c r="M22" s="40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N22" s="40"/>
       <c r="O22" s="40"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="41" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="R22" s="40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S22" s="40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="T22" s="40"/>
       <c r="U22" s="42"/>
     </row>
     <row r="23" spans="1:21" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" s="40"/>
       <c r="D23" s="40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
@@ -8643,13 +8629,13 @@
       <c r="N23" s="40"/>
       <c r="O23" s="40"/>
       <c r="P23" s="41" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q23" s="41" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="R23" s="40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="S23" s="40"/>
       <c r="T23" s="40"/>
@@ -8657,14 +8643,14 @@
     </row>
     <row r="24" spans="1:21" s="30" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E24" s="40"/>
       <c r="F24" s="40"/>
@@ -8679,10 +8665,10 @@
       <c r="O24" s="40"/>
       <c r="P24" s="41"/>
       <c r="Q24" s="41" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="R24" s="40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="S24" s="40"/>
       <c r="T24" s="40"/>
@@ -8690,20 +8676,20 @@
     </row>
     <row r="25" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="40"/>
       <c r="G25" s="40"/>
       <c r="H25" s="40" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I25" s="40"/>
       <c r="J25" s="40"/>
@@ -8715,7 +8701,7 @@
       <c r="P25" s="41"/>
       <c r="Q25" s="41"/>
       <c r="R25" s="40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S25" s="40"/>
       <c r="T25" s="40"/>
@@ -8723,20 +8709,20 @@
     </row>
     <row r="26" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E26" s="40"/>
       <c r="F26" s="40"/>
       <c r="G26" s="40"/>
       <c r="H26" s="40" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I26" s="40"/>
       <c r="J26" s="40"/>
@@ -8748,7 +8734,7 @@
       <c r="P26" s="41"/>
       <c r="Q26" s="41"/>
       <c r="R26" s="40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="S26" s="40"/>
       <c r="T26" s="40"/>
@@ -8756,20 +8742,20 @@
     </row>
     <row r="27" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
       <c r="G27" s="40"/>
       <c r="H27" s="40" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I27" s="40"/>
       <c r="J27" s="40"/>
@@ -8781,7 +8767,7 @@
       <c r="P27" s="41"/>
       <c r="Q27" s="41"/>
       <c r="R27" s="40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="S27" s="40"/>
       <c r="T27" s="40"/>
@@ -8790,12 +8776,12 @@
     <row r="28" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39"/>
       <c r="B28" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
       <c r="E28" s="40" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="40"/>
@@ -8805,17 +8791,17 @@
       <c r="K28" s="40"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N28" s="40"/>
       <c r="O28" s="40"/>
       <c r="P28" s="41"/>
       <c r="Q28" s="41"/>
       <c r="R28" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S28" s="40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="T28" s="40"/>
       <c r="U28" s="42"/>
@@ -8823,14 +8809,14 @@
     <row r="29" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39"/>
       <c r="B29" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29" s="40"/>
       <c r="D29" s="40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
@@ -8840,17 +8826,17 @@
       <c r="K29" s="40"/>
       <c r="L29" s="40"/>
       <c r="M29" s="40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N29" s="40"/>
       <c r="O29" s="40"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="41"/>
       <c r="R29" s="40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S29" s="40" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="T29" s="40"/>
       <c r="U29" s="42"/>
@@ -8858,14 +8844,14 @@
     <row r="30" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="39"/>
       <c r="B30" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
@@ -8875,19 +8861,19 @@
       <c r="K30" s="40"/>
       <c r="L30" s="40"/>
       <c r="M30" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N30" s="40"/>
       <c r="O30" s="40"/>
       <c r="P30" s="41" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q30" s="41"/>
       <c r="R30" s="40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S30" s="40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T30" s="40"/>
       <c r="U30" s="42"/>
@@ -8895,14 +8881,14 @@
     <row r="31" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="43"/>
       <c r="B31" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
@@ -8912,19 +8898,19 @@
       <c r="K31" s="44"/>
       <c r="L31" s="44"/>
       <c r="M31" s="44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N31" s="44"/>
       <c r="O31" s="44"/>
       <c r="P31" s="45" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q31" s="45"/>
       <c r="R31" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="S31" s="40" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="T31" s="44"/>
       <c r="U31" s="72"/>
@@ -8936,7 +8922,7 @@
       </c>
       <c r="C32" s="44"/>
       <c r="D32" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E32" s="44"/>
       <c r="F32" s="44"/>
@@ -8950,11 +8936,11 @@
       <c r="N32" s="44"/>
       <c r="O32" s="44"/>
       <c r="P32" s="45" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q32" s="45"/>
       <c r="R32" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="S32" s="44"/>
       <c r="T32" s="44"/>
@@ -8962,17 +8948,17 @@
     </row>
     <row r="33" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F33" s="44"/>
       <c r="G33" s="44"/>
@@ -8983,78 +8969,78 @@
       <c r="L33" s="44"/>
       <c r="M33" s="44"/>
       <c r="N33" s="44" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O33" s="44" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P33" s="45" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q33" s="45"/>
       <c r="R33" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S33" s="44" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="T33" s="44"/>
       <c r="U33" s="72"/>
     </row>
     <row r="34" spans="1:21" s="30" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F34" s="40"/>
       <c r="G34" s="40"/>
       <c r="H34" s="40"/>
       <c r="I34" s="40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J34" s="40"/>
       <c r="K34" s="40"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
       <c r="N34" s="45" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O34" s="41" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P34" s="45"/>
       <c r="Q34" s="45"/>
       <c r="R34" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S34" s="44" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T34" s="40"/>
       <c r="U34" s="42"/>
     </row>
     <row r="35" spans="1:21" s="30" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C35" s="40"/>
       <c r="D35" s="40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F35" s="40"/>
       <c r="G35" s="40"/>
@@ -9065,20 +9051,20 @@
       <c r="L35" s="40"/>
       <c r="M35" s="40"/>
       <c r="N35" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O35" s="40" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P35" s="45" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q35" s="45"/>
       <c r="R35" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S35" s="44" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T35" s="40"/>
       <c r="U35" s="42"/>
@@ -9090,7 +9076,7 @@
       </c>
       <c r="C36" s="40"/>
       <c r="D36" s="40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E36" s="40"/>
       <c r="F36" s="40"/>
@@ -9104,11 +9090,11 @@
       <c r="N36" s="40"/>
       <c r="O36" s="40"/>
       <c r="P36" s="45" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Q36" s="45"/>
       <c r="R36" s="40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
@@ -9116,17 +9102,17 @@
     </row>
     <row r="37" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
@@ -9139,37 +9125,37 @@
       <c r="N37" s="40"/>
       <c r="O37" s="40"/>
       <c r="P37" s="45" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q37" s="45"/>
       <c r="R37" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S37" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T37" s="40"/>
       <c r="U37" s="42"/>
     </row>
     <row r="38" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F38" s="40"/>
       <c r="G38" s="40"/>
       <c r="H38" s="40"/>
       <c r="I38" s="40" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
@@ -9180,27 +9166,27 @@
       <c r="P38" s="41"/>
       <c r="Q38" s="41"/>
       <c r="R38" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S38" s="44" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="T38" s="40"/>
       <c r="U38" s="42"/>
     </row>
     <row r="39" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" s="44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F39" s="44"/>
       <c r="G39" s="44"/>
@@ -9215,10 +9201,10 @@
       <c r="P39" s="45"/>
       <c r="Q39" s="45"/>
       <c r="R39" s="44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S39" s="44" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="T39" s="44"/>
       <c r="U39" s="72"/>
@@ -9252,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -9260,7 +9246,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -9302,66 +9288,66 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="E2" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="E3" s="18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="D5" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>124</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -9386,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -9394,7 +9380,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -9417,74 +9403,74 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>188</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>191</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C6" s="36"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C7" s="36"/>
     </row>
@@ -9510,7 +9496,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -9518,7 +9504,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
